--- a/docs/pension_data_combined_2026-06-12.xlsx
+++ b/docs/pension_data_combined_2026-06-12.xlsx
@@ -1246,7 +1246,7 @@
         <v>2.1256</v>
       </c>
       <c r="D49" t="n">
-        <v>84949581.78</v>
+        <v>84948724.47</v>
       </c>
     </row>
     <row r="50">
@@ -1354,7 +1354,7 @@
         <v>1.2044</v>
       </c>
       <c r="D55" t="n">
-        <v>68301976.42</v>
+        <v>68227898.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/pension_data_combined_2026-06-12.xlsx
+++ b/docs/pension_data_combined_2026-06-12.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1278</v>
-      </c>
       <c r="D48" t="n">
         <v>3869953.2</v>
       </c>
